--- a/data/permits.xlsx
+++ b/data/permits.xlsx
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45780</v>
+        <v>45783</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46218</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46005</v>
+        <v>46008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="4">
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46043</v>
+        <v>46046</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46163</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="5">
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46373</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="6">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46473</v>
+        <v>46476</v>
       </c>
     </row>
     <row r="7">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45945</v>
+        <v>45948</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46203</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="8">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45808</v>
+        <v>45811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46263</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="9">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45900</v>
+        <v>45903</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46326</v>
       </c>
     </row>
   </sheetData>
